--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post DFS_HRM-2031-0272/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post DFS_HRM-2031-0272/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,17 +434,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Dimple</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -456,26 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.67225</v>
+        <v>16.69107</v>
       </c>
       <c r="D2" t="n">
-        <v>16.37397</v>
+        <v>15.95426</v>
       </c>
       <c r="E2" t="n">
-        <v>16.70684</v>
+        <v>16.62018</v>
       </c>
       <c r="F2" t="n">
-        <v>41.95159</v>
+        <v>21.84769</v>
       </c>
       <c r="G2" t="n">
-        <v>0.052</v>
+        <v>21.48631</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85906</v>
+        <v>34.39447</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.80681</v>
+        <v>16.70876</v>
       </c>
       <c r="D3" t="n">
-        <v>16.56671</v>
+        <v>16.10269</v>
       </c>
       <c r="E3" t="n">
-        <v>16.54949</v>
+        <v>16.42962</v>
       </c>
       <c r="F3" t="n">
-        <v>41.84378</v>
+        <v>21.71913</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05118</v>
+        <v>21.46772</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83697</v>
+        <v>34.62165</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.58144</v>
+        <v>17.16088</v>
       </c>
       <c r="D4" t="n">
-        <v>16.93444</v>
+        <v>15.9986</v>
       </c>
       <c r="E4" t="n">
-        <v>16.47818</v>
+        <v>16.00532</v>
       </c>
       <c r="F4" t="n">
-        <v>42.58326</v>
+        <v>21.48771</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04988</v>
+        <v>22.08998</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82526</v>
+        <v>34.56091</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.73536</v>
+        <v>16.83473</v>
       </c>
       <c r="D5" t="n">
-        <v>16.6982</v>
+        <v>15.92203</v>
       </c>
       <c r="E5" t="n">
-        <v>16.54977</v>
+        <v>16.16569</v>
       </c>
       <c r="F5" t="n">
-        <v>42.49009</v>
+        <v>21.86321</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05103</v>
+        <v>21.65896</v>
       </c>
       <c r="H5" t="n">
-        <v>1.83882</v>
+        <v>34.91959</v>
       </c>
     </row>
     <row r="6">
@@ -559,10 +559,23 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>scratched - not measurable</t>
-        </is>
+      <c r="C6" t="n">
+        <v>16.50602</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16.24736</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16.45522</v>
+      </c>
+      <c r="F6" t="n">
+        <v>21.75886</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22.29884</v>
+      </c>
+      <c r="H6" t="n">
+        <v>34.7986</v>
       </c>
     </row>
     <row r="7">
@@ -572,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.47413</v>
+        <v>16.93586</v>
       </c>
       <c r="D7" t="n">
-        <v>16.97722</v>
+        <v>15.90624</v>
       </c>
       <c r="E7" t="n">
-        <v>16.80257</v>
+        <v>16.18895</v>
       </c>
       <c r="F7" t="n">
-        <v>43.1415</v>
+        <v>21.97452</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05004</v>
+        <v>22.0548</v>
       </c>
       <c r="H7" t="n">
-        <v>1.83337</v>
+        <v>34.20673</v>
       </c>
     </row>
     <row r="8">
@@ -597,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.91823</v>
+        <v>16.73678</v>
       </c>
       <c r="D8" t="n">
-        <v>16.51802</v>
+        <v>15.86317</v>
       </c>
       <c r="E8" t="n">
-        <v>16.35667</v>
+        <v>15.94755</v>
       </c>
       <c r="F8" t="n">
-        <v>42.43056</v>
+        <v>22.07379</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05175</v>
+        <v>21.91445</v>
       </c>
       <c r="H8" t="n">
-        <v>1.80713</v>
+        <v>34.51542</v>
       </c>
     </row>
     <row r="9">
@@ -622,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.70076</v>
+        <v>16.90888</v>
       </c>
       <c r="D9" t="n">
-        <v>16.48185</v>
+        <v>16.14713</v>
       </c>
       <c r="E9" t="n">
-        <v>16.69394</v>
+        <v>16.282</v>
       </c>
       <c r="F9" t="n">
-        <v>42.67301</v>
+        <v>21.68035</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05106</v>
+        <v>21.63431</v>
       </c>
       <c r="H9" t="n">
-        <v>1.83572</v>
+        <v>33.74513</v>
       </c>
     </row>
     <row r="10">
@@ -647,257 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.34849</v>
+        <v>16.66422</v>
       </c>
       <c r="D10" t="n">
-        <v>16.71627</v>
+        <v>15.55089</v>
       </c>
       <c r="E10" t="n">
-        <v>16.67277</v>
+        <v>16.50579</v>
       </c>
       <c r="F10" t="n">
-        <v>42.9244</v>
+        <v>22.09194</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05022</v>
+        <v>22.04717</v>
       </c>
       <c r="H10" t="n">
-        <v>1.78754</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Trace 1</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>16.8854</v>
-      </c>
-      <c r="D12" t="n">
-        <v>15.58555</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.25721</v>
-      </c>
-      <c r="F12" t="n">
-        <v>21.3888</v>
-      </c>
-      <c r="G12" t="n">
-        <v>34.06086</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>16.43612</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.21865</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.49116</v>
-      </c>
-      <c r="F13" t="n">
-        <v>21.70757</v>
-      </c>
-      <c r="G13" t="n">
-        <v>35.19886</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>re-measured</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>16.55985</v>
-      </c>
-      <c r="D14" t="n">
-        <v>16.17957</v>
-      </c>
-      <c r="E14" t="n">
-        <v>16.4965</v>
-      </c>
-      <c r="F14" t="n">
-        <v>21.89319</v>
-      </c>
-      <c r="G14" t="n">
-        <v>34.48282</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>16.6042</v>
-      </c>
-      <c r="D15" t="n">
-        <v>16.13353</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.13295</v>
-      </c>
-      <c r="F15" t="n">
-        <v>21.91258</v>
-      </c>
-      <c r="G15" t="n">
-        <v>33.25676</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>17.02588</v>
-      </c>
-      <c r="D16" t="n">
-        <v>15.98583</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.52859</v>
-      </c>
-      <c r="F16" t="n">
-        <v>22.1927</v>
-      </c>
-      <c r="G16" t="n">
-        <v>34.97443</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>16.87342</v>
-      </c>
-      <c r="D17" t="n">
-        <v>16.31528</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.69795</v>
-      </c>
-      <c r="F17" t="n">
-        <v>21.58998</v>
-      </c>
-      <c r="G17" t="n">
-        <v>33.2332</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>16.85014</v>
-      </c>
-      <c r="D18" t="n">
-        <v>15.75557</v>
-      </c>
-      <c r="E18" t="n">
-        <v>16.70704</v>
-      </c>
-      <c r="F18" t="n">
-        <v>21.46912</v>
-      </c>
-      <c r="G18" t="n">
-        <v>33.87818</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>16.70965</v>
-      </c>
-      <c r="D19" t="n">
-        <v>16.12942</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.4944</v>
-      </c>
-      <c r="F19" t="n">
-        <v>21.76533</v>
-      </c>
-      <c r="G19" t="n">
-        <v>34.59344</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>16.87966</v>
-      </c>
-      <c r="D20" t="n">
-        <v>15.94594</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.12149</v>
-      </c>
-      <c r="F20" t="n">
-        <v>21.65909</v>
-      </c>
-      <c r="G20" t="n">
-        <v>34.21498</v>
+        <v>34.62735</v>
       </c>
     </row>
   </sheetData>
